--- a/public/templates/mau-hoc-vien.xlsx
+++ b/public/templates/mau-hoc-vien.xlsx
@@ -544,7 +544,7 @@
         <v>Bị hen suyễn nhẹ, cần lưu ý khi vận động</v>
       </c>
       <c r="X2" t="str">
-        <v>Đăng ký qua campaign 20 suất miễn phí 23/05</v>
+        <v>Đăng ký qua campaign 24 suất miễn phí 23/05</v>
       </c>
     </row>
     <row r="3">
